--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487074_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487074_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.0955</v>
+        <v>9.3773</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9387</v>
+        <v>6.5149</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1568</v>
+        <v>2.8624</v>
       </c>
       <c r="G2" t="n">
         <v>5.2296</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1893</v>
+        <v>1.471</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8172</v>
+        <v>1.3934</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3721</v>
+        <v>0.0776</v>
       </c>
       <c r="V2" t="n">
         <v>3.6417</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9612</v>
+        <v>4.8725</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0522</v>
+        <v>1.91</v>
       </c>
       <c r="F3" t="n">
-        <v>2.909</v>
+        <v>2.9625</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9307</v>
@@ -688,13 +688,13 @@
         <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0776</v>
+        <v>1.9889</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5052</v>
+        <v>1.363</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5724</v>
+        <v>0.6259</v>
       </c>
       <c r="V3" t="n">
         <v>1.8842</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2106</v>
+        <v>3.5082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5108</v>
+        <v>2.7841</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6997</v>
+        <v>0.7241</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2978</v>
+        <v>2.113</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3796</v>
+        <v>0.6364</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9182</v>
+        <v>1.4766</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3795</v>
+        <v>3.3352</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2496</v>
+        <v>2.6597</v>
       </c>
       <c r="L4" t="n">
-        <v>0.13</v>
+        <v>0.6755</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0817</v>
+        <v>-1.2222</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.87</v>
+        <v>-2.0233</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7883</v>
+        <v>0.8011</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3161</v>
+        <v>-0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.0182</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7021</v>
+        <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6571</v>
+        <v>0.4604</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0061</v>
+        <v>-0.1348</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6511</v>
+        <v>0.5952</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5717</v>
+        <v>1.5138</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1435</v>
+        <v>1.5138</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>J. FERRANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1344</v>
+        <v>2.2518</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3836</v>
+        <v>1.0484</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7509</v>
+        <v>1.2033</v>
       </c>
       <c r="G5" t="n">
-        <v>2.113</v>
+        <v>-0.131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6364</v>
+        <v>-2.1352</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4766</v>
+        <v>2.0042</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3352</v>
+        <v>-0.2044</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6597</v>
+        <v>-1.5474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6755</v>
+        <v>1.3431</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2222</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0233</v>
+        <v>-0.5878</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8011</v>
+        <v>0.6612</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0866</v>
+        <v>0.1897</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5354</v>
+        <v>0.2178</v>
       </c>
       <c r="U5" t="n">
-        <v>0.622</v>
+        <v>-0.0281</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5138</v>
+        <v>1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5138</v>
+        <v>1.228</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. FERRANDEZ FERNANDEZ</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6172</v>
+        <v>2.0654</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5477</v>
+        <v>0.3294</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0695</v>
+        <v>1.736</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.131</v>
+        <v>2.2978</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1352</v>
+        <v>1.3796</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0042</v>
+        <v>0.9182</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2044</v>
+        <v>3.3795</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.5474</v>
+        <v>3.2496</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3431</v>
+        <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07340000000000001</v>
+        <v>-1.0817</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5878</v>
+        <v>-1.87</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6612</v>
+        <v>0.7883</v>
       </c>
       <c r="P6" t="n">
-        <v>0.965</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.193</v>
+        <v>-5.0182</v>
       </c>
       <c r="R6" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4449</v>
+        <v>1.512</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2829</v>
+        <v>0.8246</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.162</v>
+        <v>0.6874</v>
       </c>
       <c r="V6" t="n">
-        <v>1.228</v>
+        <v>0.5717</v>
       </c>
       <c r="W6" t="n">
-        <v>1.228</v>
+        <v>1.1435</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>E. BONILLA HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1854</v>
+        <v>1.9966</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6321</v>
+        <v>1.6093</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4467</v>
+        <v>0.3873</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7769</v>
+        <v>1.4144</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6933</v>
+        <v>1.8393</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4702</v>
+        <v>-0.4248</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5448</v>
+        <v>0.9603</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8694</v>
+        <v>2.1734</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6755</v>
+        <v>-1.2131</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.768</v>
+        <v>0.4541</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5627</v>
+        <v>-0.3341</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7947</v>
+        <v>0.7883</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7371</v>
+        <v>2.7021</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1428</v>
+        <v>1.166</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0873</v>
+        <v>1.1931</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.23</v>
+        <v>-0.0271</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1857</v>
+        <v>-2.1278</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1857</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. BONILLA HERNANDEZ</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5491</v>
+        <v>1.9667</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4295</v>
+        <v>2.0922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1196</v>
+        <v>-0.1254</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4144</v>
+        <v>0.7769</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8393</v>
+        <v>-0.6933</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4248</v>
+        <v>1.4702</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9603</v>
+        <v>1.5448</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1734</v>
+        <v>0.8694</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2131</v>
+        <v>0.6755</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4541</v>
+        <v>-0.768</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3341</v>
+        <v>-1.5627</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7883</v>
+        <v>0.7947</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7021</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2816</v>
+        <v>0.6385</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0132</v>
+        <v>0.5473</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2948</v>
+        <v>0.0912</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1278</v>
+        <v>-1.1857</v>
       </c>
       <c r="W8" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7418</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5664</v>
+        <v>-0.3726</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3622</v>
+        <v>-1.3826</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7958</v>
+        <v>1.0099</v>
       </c>
       <c r="G9" t="n">
         <v>0.7289</v>
@@ -1156,13 +1156,13 @@
         <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8514</v>
+        <v>0.3424</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4759</v>
+        <v>0.5037</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3755</v>
+        <v>-0.1613</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2859</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6342</v>
+        <v>-2.2208</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5206</v>
+        <v>-1.4016</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1136</v>
+        <v>-0.8192</v>
       </c>
       <c r="G10" t="n">
         <v>0.3783</v>
@@ -1234,13 +1234,13 @@
         <v>2.8951</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0126</v>
+        <v>0.4009</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3385</v>
+        <v>0.4574</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.351</v>
+        <v>-0.0565</v>
       </c>
       <c r="V10" t="n">
         <v>-1.842</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>22.5528</v>
+        <v>23.4451</v>
       </c>
       <c r="E11" t="n">
-        <v>12.6118</v>
+        <v>13.5041</v>
       </c>
       <c r="F11" t="n">
-        <v>9.940999999999999</v>
+        <v>9.940899999999999</v>
       </c>
       <c r="G11" t="n">
         <v>11.8772</v>
@@ -1303,7 +1303,7 @@
         <v>7.947000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0002000000000004221</v>
+        <v>0.0002000000000002</v>
       </c>
       <c r="Q11" t="n">
         <v>-19.3007</v>
@@ -1312,16 +1312,16 @@
         <v>19.3008</v>
       </c>
       <c r="S11" t="n">
-        <v>7.2773</v>
+        <v>8.1698</v>
       </c>
       <c r="T11" t="n">
-        <v>5.4733</v>
+        <v>6.365500000000001</v>
       </c>
       <c r="U11" t="n">
         <v>1.8043</v>
       </c>
       <c r="V11" t="n">
-        <v>3.398</v>
+        <v>3.397999999999999</v>
       </c>
       <c r="W11" t="n">
         <v>12.7248</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1236</v>
+        <v>2.7902</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9276</v>
+        <v>5.3268</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.804</v>
+        <v>-2.5366</v>
       </c>
       <c r="G12" t="n">
         <v>1.9517</v>
@@ -1390,13 +1390,13 @@
         <v>1.158</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0139</v>
+        <v>-0.3196</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8593</v>
+        <v>0.2585</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8454</v>
+        <v>-0.578</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3933</v>
+        <v>-0.1593</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5613</v>
+        <v>-0.4612</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1681</v>
+        <v>0.3019</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5116000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0397</v>
+        <v>-0.8057</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0278</v>
+        <v>0.1279</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0675</v>
+        <v>-0.9337</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. YAILO</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5848</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6021</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0173</v>
+        <v>0.0273</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.003</v>
+        <v>-1.1879</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9231</v>
+        <v>2.2915</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9261</v>
+        <v>-3.4794</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6653</v>
+        <v>0.9812</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6246</v>
+        <v>4.295</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0407</v>
+        <v>-3.3137</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6683</v>
+        <v>-2.1692</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7015</v>
+        <v>-2.0035</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9668</v>
+        <v>-0.1657</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.3161</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.7902</v>
+        <v>-4.8252</v>
       </c>
       <c r="R14" t="n">
-        <v>3.4741</v>
+        <v>3.0881</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5486</v>
+        <v>-1.2628</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7232</v>
+        <v>-0.657</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1745</v>
+        <v>-0.6058</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1857</v>
+        <v>3.398</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7997</v>
+        <v>3.6839</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.614</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. CAMARA</t>
+          <t>A. YAILO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-1.4199</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1791</v>
+        <v>-2.3031</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0043</v>
+        <v>0.8831</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1962</v>
+        <v>-0.003</v>
       </c>
       <c r="H15" t="n">
-        <v>0.028</v>
+        <v>0.9231</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2242</v>
+        <v>-0.9261</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2249</v>
+        <v>1.6653</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1435</v>
+        <v>1.6246</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4211</v>
+        <v>-1.6683</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1155</v>
+        <v>-0.7015</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3056</v>
+        <v>-0.9668</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>-5.7902</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5091</v>
+        <v>3.4741</v>
       </c>
       <c r="S15" t="n">
-        <v>0.657</v>
+        <v>-0.2865</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6637</v>
+        <v>0.0222</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0067</v>
+        <v>-0.3087</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8999</v>
+        <v>1.1857</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1857</v>
+        <v>1.7997</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.0856</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>L. CAMARA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8583</v>
+        <v>-1.8348</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6182</v>
+        <v>-0.3216</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2401</v>
+        <v>-1.5132</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1879</v>
+        <v>-0.1962</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2915</v>
+        <v>0.028</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.4794</v>
+        <v>-0.2242</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9812</v>
+        <v>1.2249</v>
       </c>
       <c r="K16" t="n">
-        <v>4.295</v>
+        <v>1.1435</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.3137</v>
+        <v>0.0814</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1692</v>
+        <v>-1.4211</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0035</v>
+        <v>-1.1155</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1657</v>
+        <v>-0.3056</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7371</v>
+        <v>-0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.8252</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0881</v>
+        <v>2.5091</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.3313</v>
+        <v>-0.3526</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4581</v>
+        <v>0.163</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8732</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>3.398</v>
+        <v>-0.8999</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6839</v>
+        <v>1.1857</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2859</v>
+        <v>-2.0856</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.916</v>
+        <v>-1.9894</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4224</v>
+        <v>-0.5226</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4936</v>
+        <v>-1.4668</v>
       </c>
       <c r="G17" t="n">
         <v>-2.8206</v>
@@ -1780,13 +1780,13 @@
         <v>1.7371</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5466</v>
+        <v>-0.62</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0766</v>
+        <v>-0.1768</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.47</v>
+        <v>-0.4432</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.846</v>
+        <v>-2.7994</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1442</v>
+        <v>-1.0441</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7018</v>
+        <v>-1.7553</v>
       </c>
       <c r="G18" t="n">
         <v>-0.536</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7033</v>
+        <v>-0.6567</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2974</v>
+        <v>-0.1973</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4059</v>
+        <v>-0.4594</v>
       </c>
       <c r="V18" t="n">
         <v>-1.7997</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.8923</v>
+        <v>-4.0707</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.6261</v>
+        <v>-3.1254</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2662</v>
+        <v>-0.9453</v>
       </c>
       <c r="G19" t="n">
         <v>-4.1448</v>
@@ -1936,13 +1936,13 @@
         <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6425</v>
+        <v>-0.8209</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0562</v>
+        <v>-0.5555</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5863</v>
+        <v>-0.2654</v>
       </c>
       <c r="V19" t="n">
         <v>-1.228</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ARRIBAS RODRIGUEZ</t>
+          <t>W. DIAZ GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.0334</v>
+        <v>-5.7056</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4799</v>
+        <v>-3.293</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5535</v>
+        <v>-2.4126</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6407</v>
+        <v>-1.788</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8921</v>
+        <v>-1.1012</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7486</v>
+        <v>-0.6869</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2524</v>
+        <v>-0.0726</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0828</v>
+        <v>-0.0726</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3352</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3883</v>
+        <v>-1.7155</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9749</v>
+        <v>-1.0286</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4134</v>
+        <v>-0.6869</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5441</v>
+        <v>-0.386</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6207</v>
+        <v>-0.9911</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2974</v>
+        <v>-0.5919</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3232</v>
+        <v>-0.3993</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.228</v>
+        <v>-2.5404</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6985</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.228</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. DIAZ GONZALEZ</t>
+          <t>D. ARRIBAS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.3273</v>
+        <v>-5.9065</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5934</v>
+        <v>-3.3798</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7339</v>
+        <v>-2.5267</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.788</v>
+        <v>-2.6407</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1012</v>
+        <v>-0.8921</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6869</v>
+        <v>-1.7486</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0726</v>
+        <v>-1.2524</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0726</v>
+        <v>0.0828</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.3352</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7155</v>
+        <v>-1.3883</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0286</v>
+        <v>-0.9749</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6869</v>
+        <v>-0.4134</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.386</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6128</v>
+        <v>-0.4938</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8923</v>
+        <v>-0.1973</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7205</v>
+        <v>-0.2965</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.5404</v>
+        <v>-1.228</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6985</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.842</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="22">
@@ -2125,25 +2125,25 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-22.5529</v>
+        <v>-21.8852</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.940899999999999</v>
+        <v>-9.940999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-12.612</v>
+        <v>-11.9442</v>
       </c>
       <c r="G22" t="n">
         <v>-11.8771</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3672999999999998</v>
+        <v>-0.3673000000000003</v>
       </c>
       <c r="I22" t="n">
         <v>-11.5099</v>
       </c>
       <c r="J22" t="n">
-        <v>1.837400000000001</v>
+        <v>1.8374</v>
       </c>
       <c r="K22" t="n">
         <v>9.784600000000001</v>
@@ -2161,7 +2161,7 @@
         <v>-3.5631</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.0001000000000003221</v>
+        <v>-0.0001000000000004331</v>
       </c>
       <c r="Q22" t="n">
         <v>-19.3007</v>
@@ -2170,16 +2170,16 @@
         <v>19.3007</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.277400000000001</v>
+        <v>-6.6097</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.804</v>
+        <v>-1.8042</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.4732</v>
+        <v>-4.8056</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.3982</v>
+        <v>-3.398199999999999</v>
       </c>
       <c r="W22" t="n">
         <v>9.326600000000001</v>
